--- a/data/trans_dic/IP16A06-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 5,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,81</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,28</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,05</t>
+          <t>0,0; 14,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,4</t>
+          <t>0,0; 17,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,69</t>
+          <t>1,2; 11,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,92</t>
+          <t>0,0; 14,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 18,5</t>
+          <t>1,92; 15,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,17</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>0,0; 11,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 18,69</t>
+          <t>2,23; 20,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,36</t>
+          <t>0,0; 15,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,94</t>
+          <t>1,52; 8,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 14,13</t>
+          <t>2,9; 13,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,83</t>
+          <t>0,92; 8,38</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,53</t>
+          <t>0,48; 4,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,88</t>
+          <t>0,43; 4,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,91</t>
+          <t>0,84; 5,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,56</t>
+          <t>0,37; 3,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,73</t>
+          <t>0,4; 3,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,64</t>
+          <t>0,91; 3,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,01</t>
+          <t>0,7; 2,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,07</t>
+          <t>0,36; 2,03</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3353</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3334</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3368</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3450</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3523</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3342</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1278</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3171</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4262</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>556; 5157</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2292</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4959</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4514</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>676; 5471</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4099</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4358</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>726; 6622</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4325</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1065; 6170</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1962; 8957</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>580; 5301</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2947</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5256</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>600; 5792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>801; 7718</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3906</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1203; 7641</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>717; 7266</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>592; 5602</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2455; 9969</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2647; 10913</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1113; 6298</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A06-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Edad-trans_dic.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,85</t>
+          <t>0,0; 10,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,16</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,77</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,74</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,09</t>
+          <t>0,0; 13,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,86</t>
+          <t>0,0; 17,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,12</t>
+          <t>1,17; 11,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,78</t>
+          <t>0,0; 14,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 15,56</t>
+          <t>1,91; 16,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,31</t>
+          <t>0,0; 10,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,05</t>
+          <t>0,0; 11,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 20,34</t>
+          <t>2,13; 18,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,99</t>
+          <t>0,0; 14,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,82</t>
+          <t>0,95; 8,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 13,23</t>
+          <t>3,13; 14,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,38</t>
+          <t>0,93; 8,81</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,62</t>
+          <t>0,48; 4,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,13</t>
+          <t>0,44; 4,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,31</t>
+          <t>0,85; 5,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,79</t>
+          <t>0,36; 3,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,78</t>
+          <t>0,39; 3,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,7</t>
+          <t>0,91; 3,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,88</t>
+          <t>0,69; 2,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,03</t>
+          <t>0,36; 2,11</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3353</t>
+          <t>0; 3281</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3334</t>
+          <t>0; 3272</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3368</t>
+          <t>0; 3653</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3450</t>
+          <t>0; 3568</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3523</t>
+          <t>0; 3881</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3342</t>
+          <t>0; 3541</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3171</t>
+          <t>0; 3030</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4262</t>
+          <t>0; 4201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>556; 5157</t>
+          <t>544; 5211</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4514</t>
+          <t>0; 4364</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>676; 5471</t>
+          <t>672; 5975</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4099</t>
+          <t>0; 3803</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4358</t>
+          <t>0; 4389</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>726; 6622</t>
+          <t>694; 5962</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4325</t>
+          <t>0; 4043</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1065; 6170</t>
+          <t>666; 6098</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1962; 8957</t>
+          <t>2119; 9825</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>580; 5301</t>
+          <t>589; 5578</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>600; 5792</t>
+          <t>597; 5896</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>801; 7718</t>
+          <t>816; 7603</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 4043</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1203; 7641</t>
+          <t>1217; 7719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>717; 7266</t>
+          <t>691; 6602</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>592; 5602</t>
+          <t>584; 5067</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2455; 9969</t>
+          <t>2461; 9327</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2647; 10913</t>
+          <t>2626; 11063</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1113; 6298</t>
+          <t>1107; 6564</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A06-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Edad-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -635,22 +635,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,9%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,46</t>
+          <t>0,0; 18,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,6</t>
+          <t>0,0; 14,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,24</t>
+          <t>1,18; 11,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6,52%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,15%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,29</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 16,99</t>
+          <t>2,11; 18,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,49</t>
+          <t>0,0; 14,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,13</t>
+          <t>0,0; 15,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 18,31</t>
+          <t>1,93; 18,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,95</t>
+          <t>0,0; 11,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,71</t>
+          <t>0,86; 8,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 14,51</t>
+          <t>3,1; 14,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,81</t>
+          <t>0,95; 8,83</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,7</t>
+          <t>0,82; 4,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,07</t>
+          <t>0,36; 3,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,4; 3,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,36</t>
+          <t>0,48; 4,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,45</t>
+          <t>0,43; 3,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,42</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,46</t>
+          <t>0,97; 3,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,92</t>
+          <t>0,7; 3,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,11</t>
+          <t>0,34; 2,07</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3195</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3281</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3272</t>
+          <t>0; 3649</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,27 +1527,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>656</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3472</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3653</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3568</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3774</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3881</t>
+          <t>0; 3495</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3541</t>
+          <t>0; 3044</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1690,22 +1690,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1278</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>654</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1278</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3030</t>
+          <t>0; 4391</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4201</t>
+          <t>0; 3162</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>544; 5211</t>
+          <t>548; 5422</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1805,22 +1805,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2292</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1141</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4364</t>
+          <t>0; 3835</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>672; 5975</t>
+          <t>686; 6084</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3803</t>
+          <t>0; 3884</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4389</t>
+          <t>0; 4861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>694; 5962</t>
+          <t>678; 6506</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>0; 4048</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>666; 6098</t>
+          <t>603; 6254</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2119; 9825</t>
+          <t>2102; 9569</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>589; 5578</t>
+          <t>598; 5590</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1141</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>597; 5896</t>
+          <t>1184; 7061</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>816; 7603</t>
+          <t>689; 6824</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>589; 5531</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1217; 7719</t>
+          <t>596; 5677</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>691; 6602</t>
+          <t>798; 7263</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>584; 5067</t>
+          <t>0; 3951</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2461; 9327</t>
+          <t>2610; 9806</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2626; 11063</t>
+          <t>2631; 11380</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1107; 6564</t>
+          <t>1048; 6442</t>
         </is>
       </c>
     </row>
